--- a/src/Heart_3D.xlsx
+++ b/src/Heart_3D.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F0A2F1-ADBC-4486-99DE-A78085D5DD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CA3EDD-6F21-4E69-A2B7-185AF0329BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Node_second" sheetId="39" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="265">
   <si>
     <t>Index</t>
   </si>
@@ -820,6 +820,27 @@
   </si>
   <si>
     <t>BH-&gt;His_p-&gt;His_m-&gt;His-d-&gt;RBB_m-&gt;RBB-&gt;RBB_a-&gt;RV_m-&gt;RV</t>
+  </si>
+  <si>
+    <t>sigma1sq</t>
+  </si>
+  <si>
+    <t>sigma2sq</t>
+  </si>
+  <si>
+    <t>MDP</t>
+  </si>
+  <si>
+    <t>VT_n</t>
+  </si>
+  <si>
+    <t>VR_n</t>
+  </si>
+  <si>
+    <t>VR_m</t>
+  </si>
+  <si>
+    <t>VT_m</t>
   </si>
 </sst>
 </file>
@@ -2297,10 +2318,10 @@
         <v>199</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>201</v>
+        <v>259</v>
       </c>
       <c r="J1" s="75" t="s">
         <v>184</v>
@@ -2312,13 +2333,13 @@
         <v>185</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>1</v>
+        <v>261</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>2</v>
+        <v>262</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>186</v>
@@ -2393,10 +2414,10 @@
         <v>21</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>2</v>
+        <v>263</v>
       </c>
       <c r="AO1" s="13" t="s">
-        <v>1</v>
+        <v>264</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>3</v>
@@ -47801,6 +47822,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{d1b36e95-0d50-42e9-958f-b63fa906beaa}" enabled="0" method="" siteId="{d1b36e95-0d50-42e9-958f-b63fa906beaa}" removed="1"/>
+  <clbl:label id="{b75eb9d1-7479-4f8a-9240-cc5b19dbbc64}" enabled="1" method="Standard" siteId="{d1b36e95-0d50-42e9-958f-b63fa906beaa}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>